--- a/Excel Assignment 1 - Data Exploration (1).xlsx
+++ b/Excel Assignment 1 - Data Exploration (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb57aec62d993674/Desktop/aaaaaaaa/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D6D116-7C59-4FC1-B2C7-8BC86426F049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{A6D6D116-7C59-4FC1-B2C7-8BC86426F049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F294D014-6DD3-4E21-8034-A13BBF1AA7C3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,17 @@
     <sheet name="Dataset" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -391,7 +402,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -501,7 +512,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -512,39 +523,17 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -554,49 +543,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{F14AD623-591F-4121-9EB4-755EFF74DB09}"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF4DD0E1"/>
-          <bgColor rgb="FF4DD0E1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -783,6 +729,49 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4DD0E1"/>
+          <bgColor rgb="FF4DD0E1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -797,24 +786,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{854DF8C3-9744-41DC-9553-96F08E45A860}" name="Table4" displayName="Table4" ref="B1:J35" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{854DF8C3-9744-41DC-9553-96F08E45A860}" name="Table4" displayName="Table4" ref="B1:J35" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="B1:J35" xr:uid="{854DF8C3-9744-41DC-9553-96F08E45A860}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{75956BA8-2C2F-4D42-888C-0D2B371FF9D1}" name="Product Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{9D4382E1-B36B-4CA3-9C33-2D7238EB3A5A}" name="Brand Name" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{847FA85C-F31A-4547-BB75-86477006AE1E}" name="Price ($)" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{D1971521-EBD2-482C-A4E6-7F1B5E97A46F}" name="Quantity" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{2E3D8958-8854-4D85-BAA8-6BC1E50BE9C1}" name="Category" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{F9591AAB-9368-4747-8C06-1CCF229BB3AE}" name="Price Range" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{75956BA8-2C2F-4D42-888C-0D2B371FF9D1}" name="Product Name" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{9D4382E1-B36B-4CA3-9C33-2D7238EB3A5A}" name="Brand Name" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{847FA85C-F31A-4547-BB75-86477006AE1E}" name="Price ($)" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{D1971521-EBD2-482C-A4E6-7F1B5E97A46F}" name="Quantity" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{2E3D8958-8854-4D85-BAA8-6BC1E50BE9C1}" name="Category" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{F9591AAB-9368-4747-8C06-1CCF229BB3AE}" name="Price Range" dataDxfId="3">
       <calculatedColumnFormula>IF(D2:D35&gt;=500,"High Price","Standard Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{158DA080-B6F8-44B0-9034-EBEC29CF1D5A}" name="Day" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{158DA080-B6F8-44B0-9034-EBEC29CF1D5A}" name="Day" dataDxfId="2">
       <calculatedColumnFormula>LEFT(A2,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FB0D3406-B49B-4B0F-BB90-36A1436B8700}" name="Country Code" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{FB0D3406-B49B-4B0F-BB90-36A1436B8700}" name="Country Code" dataDxfId="1">
       <calculatedColumnFormula>RIGHT(A2,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1E79E1A4-B8E9-438E-B642-4FD01CF66B67}" name="Month" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{1E79E1A4-B8E9-438E-B642-4FD01CF66B67}" name="Month" dataDxfId="0">
       <calculatedColumnFormula>MID(A2,4,3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2129,12 +2118,12 @@
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="13.36328125" customWidth="1"/>
     <col min="4" max="6" width="12.6328125" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="14.7265625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="8" max="8" width="12.6328125" customWidth="1"/>
+    <col min="9" max="9" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
@@ -2153,20 +2142,20 @@
       <c r="F1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -2185,24 +2174,24 @@
       <c r="F2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="12" t="str">
+      <c r="G2" s="6" t="str">
         <f>IF(D2:D35&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
-      <c r="H2" s="33" t="str">
+      <c r="H2" s="14" t="str">
         <f>LEFT(A2,2)</f>
         <v>28</v>
       </c>
-      <c r="I2" s="33" t="str">
+      <c r="I2" s="14" t="str">
         <f>RIGHT(A2,2)</f>
         <v>US</v>
       </c>
-      <c r="J2" s="33" t="str">
+      <c r="J2" s="14" t="str">
         <f>MID(A2,4,3)</f>
         <v>JAN</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
@@ -2221,29 +2210,27 @@
       <c r="F3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="12" t="str">
+      <c r="G3" s="6" t="str">
         <f t="shared" ref="G3:G35" si="0">IF(D3:D36&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
-      <c r="H3" s="33" t="str">
+      <c r="H3" s="14" t="str">
         <f t="shared" ref="H3:H35" si="1">LEFT(A3,2)</f>
         <v>15</v>
       </c>
-      <c r="I3" s="33" t="str">
+      <c r="I3" s="14" t="str">
         <f t="shared" ref="I3:I35" si="2">RIGHT(A3,2)</f>
         <v>US</v>
       </c>
-      <c r="J3" s="33" t="str">
+      <c r="J3" s="14" t="str">
         <f t="shared" ref="J3:J35" si="3">MID(A3,4,3)</f>
         <v>FEB</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="8"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>31</v>
       </c>
@@ -2262,27 +2249,27 @@
       <c r="F4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="36" t="str">
+      <c r="G4" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H4" s="33" t="str">
+      <c r="H4" s="14" t="str">
         <f t="shared" si="1"/>
         <v>03</v>
       </c>
-      <c r="I4" s="33" t="str">
+      <c r="I4" s="14" t="str">
         <f t="shared" si="2"/>
         <v>US</v>
       </c>
-      <c r="J4" s="33" t="str">
+      <c r="J4" s="14" t="str">
         <f t="shared" si="3"/>
         <v>MAR</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -2301,23 +2288,23 @@
       <c r="F5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="36" t="str">
+      <c r="G5" s="6" t="str">
         <f t="shared" si="0"/>
         <v>High Price</v>
       </c>
-      <c r="H5" s="33" t="str">
+      <c r="H5" s="14" t="str">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="I5" s="33" t="str">
+      <c r="I5" s="14" t="str">
         <f t="shared" si="2"/>
         <v>US</v>
       </c>
-      <c r="J5" s="33" t="str">
+      <c r="J5" s="14" t="str">
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="9" t="s">
         <v>110</v>
       </c>
       <c r="M5">
@@ -2325,7 +2312,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
@@ -2344,27 +2331,27 @@
       <c r="F6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="36" t="str">
+      <c r="G6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H6" s="33" t="str">
+      <c r="H6" s="14" t="str">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="I6" s="33" t="str">
+      <c r="I6" s="14" t="str">
         <f t="shared" si="2"/>
         <v>US</v>
       </c>
-      <c r="J6" s="33" t="str">
+      <c r="J6" s="14" t="str">
         <f t="shared" si="3"/>
         <v>MAY</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>42</v>
       </c>
@@ -2383,27 +2370,31 @@
       <c r="F7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="36" t="str">
+      <c r="G7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H7" s="33" t="str">
+      <c r="H7" s="14" t="str">
         <f t="shared" si="1"/>
         <v>07</v>
       </c>
-      <c r="I7" s="33" t="str">
+      <c r="I7" s="14" t="str">
         <f t="shared" si="2"/>
         <v>UK</v>
       </c>
-      <c r="J7" s="33" t="str">
+      <c r="J7" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="10" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N7">
+        <f>COUNTA(Table4[Product Name])</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>45</v>
       </c>
@@ -2422,27 +2413,27 @@
       <c r="F8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="36" t="str">
+      <c r="G8" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H8" s="33" t="str">
+      <c r="H8" s="14" t="str">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I8" s="33" t="str">
+      <c r="I8" s="14" t="str">
         <f t="shared" si="2"/>
         <v>UK</v>
       </c>
-      <c r="J8" s="33" t="str">
+      <c r="J8" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>48</v>
       </c>
@@ -2461,23 +2452,23 @@
       <c r="F9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="36" t="str">
+      <c r="G9" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H9" s="33" t="str">
+      <c r="H9" s="14" t="str">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="I9" s="33" t="str">
+      <c r="I9" s="14" t="str">
         <f t="shared" si="2"/>
         <v>UK</v>
       </c>
-      <c r="J9" s="33" t="str">
+      <c r="J9" s="14" t="str">
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="L9" s="8" t="s">
         <v>112</v>
       </c>
       <c r="M9">
@@ -2485,7 +2476,7 @@
         <v>297.05882352941177</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
@@ -2504,24 +2495,24 @@
       <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="36" t="str">
+      <c r="G10" s="6" t="str">
         <f t="shared" si="0"/>
         <v>High Price</v>
       </c>
-      <c r="H10" s="33" t="str">
+      <c r="H10" s="14" t="str">
         <f t="shared" si="1"/>
         <v>05</v>
       </c>
-      <c r="I10" s="33" t="str">
+      <c r="I10" s="14" t="str">
         <f t="shared" si="2"/>
         <v>UK</v>
       </c>
-      <c r="J10" s="33" t="str">
+      <c r="J10" s="14" t="str">
         <f t="shared" si="3"/>
         <v>SEP</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>54</v>
       </c>
@@ -2540,28 +2531,28 @@
       <c r="F11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="36" t="str">
+      <c r="G11" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H11" s="33" t="str">
+      <c r="H11" s="14" t="str">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="I11" s="33" t="str">
+      <c r="I11" s="14" t="str">
         <f t="shared" si="2"/>
         <v>UK</v>
       </c>
-      <c r="J11" s="33" t="str">
+      <c r="J11" s="14" t="str">
         <f t="shared" si="3"/>
         <v>OCT</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="L11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="M11" s="19"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2580,27 +2571,27 @@
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="36" t="str">
+      <c r="G12" s="6" t="str">
         <f t="shared" si="0"/>
         <v>High Price</v>
       </c>
-      <c r="H12" s="33" t="str">
+      <c r="H12" s="14" t="str">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="I12" s="33" t="str">
+      <c r="I12" s="14" t="str">
         <f t="shared" si="2"/>
         <v>IN</v>
       </c>
-      <c r="J12" s="33" t="str">
+      <c r="J12" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="L12" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>59</v>
       </c>
@@ -2619,23 +2610,23 @@
       <c r="F13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="36" t="str">
+      <c r="G13" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H13" s="33" t="str">
+      <c r="H13" s="14" t="str">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="I13" s="33" t="str">
+      <c r="I13" s="14" t="str">
         <f t="shared" si="2"/>
         <v>AU</v>
       </c>
-      <c r="J13" s="33" t="str">
+      <c r="J13" s="14" t="str">
         <f t="shared" si="3"/>
         <v>NOV</v>
       </c>
-      <c r="L13" s="17" t="s">
+      <c r="L13" s="8" t="s">
         <v>113</v>
       </c>
       <c r="M13">
@@ -2643,7 +2634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>60</v>
       </c>
@@ -2662,23 +2653,23 @@
       <c r="F14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="36" t="str">
+      <c r="G14" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H14" s="33" t="str">
+      <c r="H14" s="14" t="str">
         <f t="shared" si="1"/>
         <v>08</v>
       </c>
-      <c r="I14" s="33" t="str">
+      <c r="I14" s="14" t="str">
         <f t="shared" si="2"/>
         <v>DE</v>
       </c>
-      <c r="J14" s="33" t="str">
+      <c r="J14" s="14" t="str">
         <f t="shared" si="3"/>
         <v>DEC</v>
       </c>
-      <c r="L14" s="17" t="s">
+      <c r="L14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="M14">
@@ -2686,7 +2677,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>62</v>
       </c>
@@ -2705,24 +2696,24 @@
       <c r="F15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="36" t="str">
+      <c r="G15" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H15" s="33" t="str">
+      <c r="H15" s="14" t="str">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="I15" s="33" t="str">
+      <c r="I15" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J15" s="33" t="str">
+      <c r="J15" s="14" t="str">
         <f t="shared" si="3"/>
         <v>FEB</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>65</v>
       </c>
@@ -2741,26 +2732,26 @@
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="36" t="str">
+      <c r="G16" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H16" s="33" t="str">
+      <c r="H16" s="14" t="str">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="I16" s="33" t="str">
+      <c r="I16" s="14" t="str">
         <f t="shared" si="2"/>
         <v>ES</v>
       </c>
-      <c r="J16" s="33" t="str">
+      <c r="J16" s="14" t="str">
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
-      <c r="L16" s="23" t="s">
+      <c r="L16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="22"/>
+      <c r="M16" s="12"/>
     </row>
     <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
@@ -2781,23 +2772,23 @@
       <c r="F17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="36" t="str">
+      <c r="G17" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H17" s="33" t="str">
+      <c r="H17" s="14" t="str">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="I17" s="33" t="str">
+      <c r="I17" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J17" s="33" t="str">
+      <c r="J17" s="14" t="str">
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="L17" s="24" t="s">
+      <c r="L17" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2820,19 +2811,19 @@
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="36" t="str">
+      <c r="G18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H18" s="33" t="str">
+      <c r="H18" s="14" t="str">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="I18" s="33" t="str">
+      <c r="I18" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CN</v>
       </c>
-      <c r="J18" s="33" t="str">
+      <c r="J18" s="14" t="str">
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
@@ -2856,26 +2847,26 @@
       <c r="F19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="36" t="str">
+      <c r="G19" s="6" t="str">
         <f t="shared" si="0"/>
         <v>High Price</v>
       </c>
-      <c r="H19" s="33" t="str">
+      <c r="H19" s="14" t="str">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="I19" s="33" t="str">
+      <c r="I19" s="14" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
       </c>
-      <c r="J19" s="33" t="str">
+      <c r="J19" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JAN</v>
       </c>
-      <c r="L19" s="26" t="s">
+      <c r="L19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="25"/>
+      <c r="M19" s="12"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
@@ -2896,23 +2887,23 @@
       <c r="F20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="36" t="str">
+      <c r="G20" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H20" s="33" t="str">
+      <c r="H20" s="14" t="str">
         <f t="shared" si="1"/>
         <v>01</v>
       </c>
-      <c r="I20" s="33" t="str">
+      <c r="I20" s="14" t="str">
         <f t="shared" si="2"/>
         <v>UK</v>
       </c>
-      <c r="J20" s="33" t="str">
+      <c r="J20" s="14" t="str">
         <f t="shared" si="3"/>
         <v>MAR</v>
       </c>
-      <c r="L20" s="27" t="s">
+      <c r="L20" s="8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2935,23 +2926,23 @@
       <c r="F21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="36" t="str">
+      <c r="G21" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H21" s="33" t="str">
+      <c r="H21" s="14" t="str">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="I21" s="33" t="str">
+      <c r="I21" s="14" t="str">
         <f t="shared" si="2"/>
         <v>US</v>
       </c>
-      <c r="J21" s="33" t="str">
+      <c r="J21" s="14" t="str">
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="L21" s="10" t="s">
         <v>116</v>
       </c>
       <c r="O21">
@@ -2978,24 +2969,24 @@
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="36" t="str">
+      <c r="G22" s="6" t="str">
         <f t="shared" si="0"/>
         <v>High Price</v>
       </c>
-      <c r="H22" s="33" t="str">
+      <c r="H22" s="14" t="str">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="I22" s="33" t="str">
+      <c r="I22" s="14" t="str">
         <f t="shared" si="2"/>
         <v>RU</v>
       </c>
-      <c r="J22" s="33" t="str">
+      <c r="J22" s="14" t="str">
         <f t="shared" si="3"/>
         <v>MAY</v>
       </c>
-      <c r="K22" s="28"/>
-      <c r="L22" s="29" t="s">
+      <c r="K22" s="12"/>
+      <c r="L22" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3018,23 +3009,23 @@
       <c r="F23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="36" t="str">
+      <c r="G23" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H23" s="33" t="str">
+      <c r="H23" s="14" t="str">
         <f t="shared" si="1"/>
         <v>09</v>
       </c>
-      <c r="I23" s="33" t="str">
+      <c r="I23" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J23" s="33" t="str">
+      <c r="J23" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JAN</v>
       </c>
-      <c r="L23" s="16" t="s">
+      <c r="L23" s="10" t="s">
         <v>117</v>
       </c>
       <c r="N23">
@@ -3061,19 +3052,19 @@
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="36" t="str">
+      <c r="G24" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H24" s="33" t="str">
+      <c r="H24" s="14" t="str">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I24" s="33" t="str">
+      <c r="I24" s="14" t="str">
         <f t="shared" si="2"/>
         <v>BR</v>
       </c>
-      <c r="J24" s="33" t="str">
+      <c r="J24" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
@@ -3097,26 +3088,26 @@
       <c r="F25" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="36" t="str">
+      <c r="G25" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H25" s="33" t="str">
+      <c r="H25" s="14" t="str">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="I25" s="33" t="str">
+      <c r="I25" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J25" s="33" t="str">
+      <c r="J25" s="14" t="str">
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="L25" s="31" t="s">
+      <c r="L25" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="30"/>
+      <c r="M25" s="12"/>
     </row>
     <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
@@ -3137,23 +3128,23 @@
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="36" t="str">
+      <c r="G26" s="6" t="str">
         <f t="shared" si="0"/>
         <v>High Price</v>
       </c>
-      <c r="H26" s="33" t="str">
+      <c r="H26" s="14" t="str">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="I26" s="33" t="str">
+      <c r="I26" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J26" s="33" t="str">
+      <c r="J26" s="14" t="str">
         <f t="shared" si="3"/>
         <v>SEP</v>
       </c>
-      <c r="L26" s="32" t="s">
+      <c r="L26" s="8" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3176,23 +3167,23 @@
       <c r="F27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="36" t="str">
+      <c r="G27" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H27" s="33" t="str">
+      <c r="H27" s="14" t="str">
         <f t="shared" si="1"/>
         <v>03</v>
       </c>
-      <c r="I27" s="33" t="str">
+      <c r="I27" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J27" s="33" t="str">
+      <c r="J27" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
-      <c r="L27" s="34" t="s">
+      <c r="L27" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3215,23 +3206,23 @@
       <c r="F28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G28" s="36" t="str">
+      <c r="G28" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H28" s="33" t="str">
+      <c r="H28" s="14" t="str">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="I28" s="33" t="str">
+      <c r="I28" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J28" s="33" t="str">
+      <c r="J28" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
-      <c r="L28" s="35" t="s">
+      <c r="L28" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3254,19 +3245,19 @@
       <c r="F29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="36" t="str">
+      <c r="G29" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H29" s="33" t="str">
+      <c r="H29" s="14" t="str">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="I29" s="33" t="str">
+      <c r="I29" s="14" t="str">
         <f t="shared" si="2"/>
         <v>ES</v>
       </c>
-      <c r="J29" s="33" t="str">
+      <c r="J29" s="14" t="str">
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
@@ -3290,19 +3281,19 @@
       <c r="F30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G30" s="36" t="str">
+      <c r="G30" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H30" s="33" t="str">
+      <c r="H30" s="14" t="str">
         <f t="shared" si="1"/>
         <v>07</v>
       </c>
-      <c r="I30" s="33" t="str">
+      <c r="I30" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J30" s="33" t="str">
+      <c r="J30" s="14" t="str">
         <f t="shared" si="3"/>
         <v>MAR</v>
       </c>
@@ -3326,19 +3317,19 @@
       <c r="F31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G31" s="36" t="str">
+      <c r="G31" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H31" s="33" t="str">
+      <c r="H31" s="14" t="str">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="I31" s="33" t="str">
+      <c r="I31" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J31" s="33" t="str">
+      <c r="J31" s="14" t="str">
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
@@ -3362,19 +3353,19 @@
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="36" t="str">
+      <c r="G32" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H32" s="33" t="str">
+      <c r="H32" s="14" t="str">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="I32" s="33" t="str">
+      <c r="I32" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J32" s="33" t="str">
+      <c r="J32" s="14" t="str">
         <f t="shared" si="3"/>
         <v>MAY</v>
       </c>
@@ -3398,19 +3389,19 @@
       <c r="F33" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="36" t="str">
+      <c r="G33" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H33" s="33" t="str">
+      <c r="H33" s="14" t="str">
         <f t="shared" si="1"/>
         <v>02</v>
       </c>
-      <c r="I33" s="33" t="str">
+      <c r="I33" s="14" t="str">
         <f t="shared" si="2"/>
         <v>CA</v>
       </c>
-      <c r="J33" s="33" t="str">
+      <c r="J33" s="14" t="str">
         <f t="shared" si="3"/>
         <v>DEC</v>
       </c>
@@ -3434,19 +3425,19 @@
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="36" t="str">
+      <c r="G34" s="6" t="str">
         <f t="shared" si="0"/>
         <v>High Price</v>
       </c>
-      <c r="H34" s="33" t="str">
+      <c r="H34" s="14" t="str">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="I34" s="33" t="str">
+      <c r="I34" s="14" t="str">
         <f t="shared" si="2"/>
         <v>IN</v>
       </c>
-      <c r="J34" s="33" t="str">
+      <c r="J34" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
@@ -3470,25 +3461,25 @@
       <c r="F35" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G35" s="36" t="str">
+      <c r="G35" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Standard Price</v>
       </c>
-      <c r="H35" s="33" t="str">
+      <c r="H35" s="14" t="str">
         <f t="shared" si="1"/>
         <v>09</v>
       </c>
-      <c r="I35" s="33" t="str">
+      <c r="I35" s="14" t="str">
         <f t="shared" si="2"/>
         <v>FR</v>
       </c>
-      <c r="J35" s="33" t="str">
+      <c r="J35" s="14" t="str">
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H36" s="33" t="str">
+      <c r="H36" s="14" t="str">
         <f t="shared" ref="H36" si="4">LEFT(A36,2)</f>
         <v/>
       </c>
